--- a/subsidy-template.xlsx
+++ b/subsidy-template.xlsx
@@ -1454,14 +1454,14 @@
           <t>附件8：委托银行代发全日制在校学生劳务补助明细表</t>
         </is>
       </c>
-      <c r="B1" s="22" t="n"/>
-      <c r="C1" s="22" t="n"/>
-      <c r="D1" s="22" t="n"/>
-      <c r="E1" s="22" t="n"/>
-      <c r="F1" s="22" t="n"/>
-      <c r="G1" s="22" t="n"/>
-      <c r="H1" s="22" t="n"/>
-      <c r="I1" s="22" t="n"/>
+      <c r="B1" s="21" t="n"/>
+      <c r="C1" s="21" t="n"/>
+      <c r="D1" s="21" t="n"/>
+      <c r="E1" s="21" t="n"/>
+      <c r="F1" s="21" t="n"/>
+      <c r="G1" s="21" t="n"/>
+      <c r="H1" s="21" t="n"/>
+      <c r="I1" s="21" t="n"/>
       <c r="J1" s="23" t="n"/>
     </row>
     <row r="2" ht="20.4" customFormat="1" customHeight="1" s="1">
@@ -1482,14 +1482,14 @@
           <t xml:space="preserve">单位（盖章）：                                                            </t>
         </is>
       </c>
-      <c r="B3" s="26" t="n"/>
-      <c r="C3" s="26" t="n"/>
-      <c r="D3" s="26" t="n"/>
-      <c r="E3" s="26" t="n"/>
-      <c r="F3" s="26" t="n"/>
-      <c r="G3" s="26" t="n"/>
-      <c r="H3" s="26" t="n"/>
-      <c r="I3" s="26" t="n"/>
+      <c r="B3" s="25" t="n"/>
+      <c r="C3" s="25" t="n"/>
+      <c r="D3" s="25" t="n"/>
+      <c r="E3" s="25" t="n"/>
+      <c r="F3" s="25" t="n"/>
+      <c r="G3" s="25" t="n"/>
+      <c r="H3" s="25" t="n"/>
+      <c r="I3" s="25" t="n"/>
       <c r="J3" s="23" t="n"/>
     </row>
     <row r="4" ht="25.95" customFormat="1" customHeight="1" s="1">
@@ -1498,15 +1498,15 @@
           <t xml:space="preserve">发放事由：2026年1-2月 ☑管理工作助理 ¨学生兼职辅导员 ¨教学助理 ¨科研助理   ¨临时岗位（名称）：                                                                      </t>
         </is>
       </c>
-      <c r="B4" s="26" t="n"/>
-      <c r="C4" s="26" t="n"/>
-      <c r="D4" s="26" t="n"/>
-      <c r="E4" s="26" t="n"/>
-      <c r="F4" s="26" t="n"/>
-      <c r="G4" s="26" t="n"/>
-      <c r="H4" s="26" t="n"/>
-      <c r="I4" s="26" t="n"/>
-      <c r="J4" s="26" t="n"/>
+      <c r="B4" s="25" t="n"/>
+      <c r="C4" s="25" t="n"/>
+      <c r="D4" s="25" t="n"/>
+      <c r="E4" s="25" t="n"/>
+      <c r="F4" s="25" t="n"/>
+      <c r="G4" s="25" t="n"/>
+      <c r="H4" s="25" t="n"/>
+      <c r="I4" s="25" t="n"/>
+      <c r="J4" s="25" t="n"/>
     </row>
     <row r="5" ht="34.95" customFormat="1" customHeight="1" s="2">
       <c r="A5" s="27" t="inlineStr">
@@ -1858,13 +1858,13 @@
           <t xml:space="preserve">                                                                                        合计：</t>
         </is>
       </c>
-      <c r="B14" s="38" t="n"/>
-      <c r="C14" s="38" t="n"/>
-      <c r="D14" s="38" t="n"/>
-      <c r="E14" s="38" t="n"/>
-      <c r="F14" s="38" t="n"/>
-      <c r="G14" s="38" t="n"/>
-      <c r="H14" s="39" t="n"/>
+      <c r="B14" s="37" t="n"/>
+      <c r="C14" s="37" t="n"/>
+      <c r="D14" s="37" t="n"/>
+      <c r="E14" s="37" t="n"/>
+      <c r="F14" s="37" t="n"/>
+      <c r="G14" s="37" t="n"/>
+      <c r="H14" s="37" t="n"/>
       <c r="I14" s="40">
         <f>SUM(I6:I13)</f>
         <v/>
@@ -1877,15 +1877,15 @@
           <t>设岗单位负责人签字：                制表人签字：                制表人电话：              制表日期：2026年3月2日</t>
         </is>
       </c>
-      <c r="B15" s="42" t="n"/>
-      <c r="C15" s="42" t="n"/>
-      <c r="D15" s="42" t="n"/>
-      <c r="E15" s="42" t="n"/>
-      <c r="F15" s="42" t="n"/>
-      <c r="G15" s="42" t="n"/>
-      <c r="H15" s="42" t="n"/>
-      <c r="I15" s="42" t="n"/>
-      <c r="J15" s="42" t="n"/>
+      <c r="B15" s="41" t="n"/>
+      <c r="C15" s="41" t="n"/>
+      <c r="D15" s="41" t="n"/>
+      <c r="E15" s="41" t="n"/>
+      <c r="F15" s="41" t="n"/>
+      <c r="G15" s="41" t="n"/>
+      <c r="H15" s="41" t="n"/>
+      <c r="I15" s="41" t="n"/>
+      <c r="J15" s="41" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">

--- a/subsidy-template.xlsx
+++ b/subsidy-template.xlsx
@@ -20,7 +20,7 @@
     <numFmt numFmtId="165" formatCode="_-&quot;NT$&quot;* #,##0.00_-;\-&quot;NT$&quot;* #,##0.00_-;_-&quot;NT$&quot;* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="166" formatCode="_-&quot;NT$&quot;* #,##0_-;\-&quot;NT$&quot;* #,##0_-;_-&quot;NT$&quot;* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
-  <fonts count="41">
+  <fonts count="47">
     <font>
       <name val="Calibri"/>
       <charset val="134"/>
@@ -297,6 +297,66 @@
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="0"/>
+      <strike val="0"/>
+      <outline val="0"/>
+      <shadow val="0"/>
+      <color rgb="00000000"/>
+      <sz val="18"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="0"/>
+      <strike val="0"/>
+      <outline val="0"/>
+      <shadow val="0"/>
+      <color rgb="00000000"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="0"/>
+      <strike val="0"/>
+      <outline val="0"/>
+      <shadow val="0"/>
+      <color rgb="00000000"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="0"/>
+      <strike val="0"/>
+      <outline val="0"/>
+      <shadow val="0"/>
+      <color rgb="00000000"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="0"/>
+      <strike val="0"/>
+      <outline val="0"/>
+      <shadow val="0"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="0"/>
+      <strike val="0"/>
+      <outline val="0"/>
+      <shadow val="0"/>
+      <color rgb="00000000"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="33">
@@ -895,7 +955,7 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1017,6 +1077,111 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="35" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="45" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="45" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="45" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1449,102 +1614,102 @@
   </cols>
   <sheetData>
     <row r="1" ht="31.95" customFormat="1" customHeight="1" s="1">
-      <c r="A1" s="21" t="inlineStr">
+      <c r="A1" s="61" t="inlineStr">
         <is>
           <t>附件8：委托银行代发全日制在校学生劳务补助明细表</t>
         </is>
       </c>
-      <c r="B1" s="21" t="n"/>
-      <c r="C1" s="21" t="n"/>
-      <c r="D1" s="21" t="n"/>
-      <c r="E1" s="21" t="n"/>
-      <c r="F1" s="21" t="n"/>
-      <c r="G1" s="21" t="n"/>
-      <c r="H1" s="21" t="n"/>
-      <c r="I1" s="21" t="n"/>
-      <c r="J1" s="23" t="n"/>
+      <c r="B1" s="61" t="n"/>
+      <c r="C1" s="61" t="n"/>
+      <c r="D1" s="61" t="n"/>
+      <c r="E1" s="61" t="n"/>
+      <c r="F1" s="61" t="n"/>
+      <c r="G1" s="61" t="n"/>
+      <c r="H1" s="61" t="n"/>
+      <c r="I1" s="61" t="n"/>
+      <c r="J1" s="62" t="n"/>
     </row>
     <row r="2" ht="20.4" customFormat="1" customHeight="1" s="1">
-      <c r="A2" s="24" t="n"/>
-      <c r="B2" s="24" t="n"/>
-      <c r="C2" s="24" t="n"/>
-      <c r="D2" s="24" t="n"/>
-      <c r="E2" s="24" t="n"/>
-      <c r="F2" s="24" t="n"/>
-      <c r="G2" s="24" t="n"/>
-      <c r="H2" s="24" t="n"/>
-      <c r="I2" s="24" t="n"/>
-      <c r="J2" s="23" t="n"/>
+      <c r="A2" s="63" t="n"/>
+      <c r="B2" s="63" t="n"/>
+      <c r="C2" s="63" t="n"/>
+      <c r="D2" s="63" t="n"/>
+      <c r="E2" s="63" t="n"/>
+      <c r="F2" s="63" t="n"/>
+      <c r="G2" s="63" t="n"/>
+      <c r="H2" s="63" t="n"/>
+      <c r="I2" s="63" t="n"/>
+      <c r="J2" s="62" t="n"/>
     </row>
     <row r="3" ht="21" customFormat="1" customHeight="1" s="1">
-      <c r="A3" s="25" t="inlineStr">
+      <c r="A3" s="64" t="inlineStr">
         <is>
           <t xml:space="preserve">单位（盖章）：                                                            </t>
         </is>
       </c>
-      <c r="B3" s="25" t="n"/>
-      <c r="C3" s="25" t="n"/>
-      <c r="D3" s="25" t="n"/>
-      <c r="E3" s="25" t="n"/>
-      <c r="F3" s="25" t="n"/>
-      <c r="G3" s="25" t="n"/>
-      <c r="H3" s="25" t="n"/>
-      <c r="I3" s="25" t="n"/>
-      <c r="J3" s="23" t="n"/>
+      <c r="B3" s="64" t="n"/>
+      <c r="C3" s="64" t="n"/>
+      <c r="D3" s="64" t="n"/>
+      <c r="E3" s="64" t="n"/>
+      <c r="F3" s="64" t="n"/>
+      <c r="G3" s="64" t="n"/>
+      <c r="H3" s="64" t="n"/>
+      <c r="I3" s="64" t="n"/>
+      <c r="J3" s="62" t="n"/>
     </row>
     <row r="4" ht="25.95" customFormat="1" customHeight="1" s="1">
-      <c r="A4" s="25" t="inlineStr">
+      <c r="A4" s="64" t="inlineStr">
         <is>
           <t xml:space="preserve">发放事由：2026年1-2月 ☑管理工作助理 ¨学生兼职辅导员 ¨教学助理 ¨科研助理   ¨临时岗位（名称）：                                                                      </t>
         </is>
       </c>
-      <c r="B4" s="25" t="n"/>
-      <c r="C4" s="25" t="n"/>
-      <c r="D4" s="25" t="n"/>
-      <c r="E4" s="25" t="n"/>
-      <c r="F4" s="25" t="n"/>
-      <c r="G4" s="25" t="n"/>
-      <c r="H4" s="25" t="n"/>
-      <c r="I4" s="25" t="n"/>
-      <c r="J4" s="25" t="n"/>
+      <c r="B4" s="64" t="n"/>
+      <c r="C4" s="64" t="n"/>
+      <c r="D4" s="64" t="n"/>
+      <c r="E4" s="64" t="n"/>
+      <c r="F4" s="64" t="n"/>
+      <c r="G4" s="64" t="n"/>
+      <c r="H4" s="64" t="n"/>
+      <c r="I4" s="64" t="n"/>
+      <c r="J4" s="64" t="n"/>
     </row>
     <row r="5" ht="34.95" customFormat="1" customHeight="1" s="2">
-      <c r="A5" s="27" t="inlineStr">
+      <c r="A5" s="65" t="inlineStr">
         <is>
           <t>序号</t>
         </is>
       </c>
-      <c r="B5" s="27" t="inlineStr">
+      <c r="B5" s="65" t="inlineStr">
         <is>
           <t>学号</t>
         </is>
       </c>
-      <c r="C5" s="27" t="inlineStr">
+      <c r="C5" s="65" t="inlineStr">
         <is>
           <t>姓名</t>
         </is>
       </c>
-      <c r="D5" s="27" t="inlineStr">
+      <c r="D5" s="65" t="inlineStr">
         <is>
           <t>工作时数</t>
         </is>
       </c>
-      <c r="E5" s="27" t="inlineStr">
+      <c r="E5" s="65" t="inlineStr">
         <is>
           <t>院系</t>
         </is>
       </c>
-      <c r="F5" s="27" t="inlineStr">
+      <c r="F5" s="65" t="inlineStr">
         <is>
           <t>专业</t>
         </is>
       </c>
-      <c r="G5" s="28" t="inlineStr">
+      <c r="G5" s="65" t="inlineStr">
         <is>
           <t>本科生/研究生</t>
         </is>
       </c>
-      <c r="H5" s="29" t="inlineStr">
+      <c r="H5" s="66" t="inlineStr">
         <is>
           <t>年级</t>
         </is>
@@ -1554,338 +1719,338 @@
           <t xml:space="preserve">应发金额 </t>
         </is>
       </c>
-      <c r="J5" s="31" t="inlineStr">
+      <c r="J5" s="67" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
     <row r="6" ht="24" customFormat="1" customHeight="1" s="1">
-      <c r="A6" s="32" t="n">
+      <c r="A6" s="68" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="33" t="inlineStr">
+      <c r="B6" s="69" t="inlineStr">
         <is>
           <t>202436382952</t>
         </is>
       </c>
-      <c r="C6" s="33" t="inlineStr">
+      <c r="C6" s="69" t="inlineStr">
         <is>
           <t>李炫杰</t>
         </is>
       </c>
-      <c r="D6" s="33" t="n">
+      <c r="D6" s="69" t="n">
         <v>30</v>
       </c>
-      <c r="E6" s="33" t="inlineStr">
+      <c r="E6" s="69" t="inlineStr">
         <is>
           <t>国际商学院</t>
         </is>
       </c>
-      <c r="F6" s="33" t="inlineStr">
+      <c r="F6" s="69" t="inlineStr">
         <is>
           <t>大数据管理与应用（中外联合培养）</t>
         </is>
       </c>
-      <c r="G6" s="33" t="inlineStr">
+      <c r="G6" s="69" t="inlineStr">
         <is>
           <t>本科</t>
         </is>
       </c>
-      <c r="H6" s="33" t="n">
+      <c r="H6" s="69" t="n">
         <v>2024</v>
       </c>
-      <c r="I6" s="33" t="n">
+      <c r="I6" s="69" t="n">
         <v>711</v>
       </c>
-      <c r="J6" s="34" t="n"/>
+      <c r="J6" s="70" t="n"/>
     </row>
     <row r="7" ht="24" customFormat="1" customHeight="1" s="1">
-      <c r="A7" s="32" t="n">
+      <c r="A7" s="68" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="33" t="inlineStr">
+      <c r="B7" s="69" t="inlineStr">
         <is>
           <t>20233501036</t>
         </is>
       </c>
-      <c r="C7" s="33" t="inlineStr">
+      <c r="C7" s="69" t="inlineStr">
         <is>
           <t>郑铠亮</t>
         </is>
       </c>
-      <c r="D7" s="33" t="n">
+      <c r="D7" s="69" t="n">
         <v>7.5</v>
       </c>
-      <c r="E7" s="33" t="inlineStr">
+      <c r="E7" s="69" t="inlineStr">
         <is>
           <t>国际商学院</t>
         </is>
       </c>
-      <c r="F7" s="33" t="inlineStr">
+      <c r="F7" s="69" t="inlineStr">
         <is>
           <t>文化产业管理</t>
         </is>
       </c>
-      <c r="G7" s="33" t="inlineStr">
+      <c r="G7" s="69" t="inlineStr">
         <is>
           <t>本科</t>
         </is>
       </c>
-      <c r="H7" s="33" t="n">
+      <c r="H7" s="69" t="n">
         <v>2023</v>
       </c>
-      <c r="I7" s="33" t="n">
+      <c r="I7" s="69" t="n">
         <v>178</v>
       </c>
-      <c r="J7" s="34" t="n"/>
+      <c r="J7" s="70" t="n"/>
     </row>
     <row r="8" ht="24" customFormat="1" customHeight="1" s="1">
-      <c r="A8" s="32" t="n">
+      <c r="A8" s="68" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="33" t="inlineStr">
+      <c r="B8" s="69" t="inlineStr">
         <is>
           <t>20233637045</t>
         </is>
       </c>
-      <c r="C8" s="33" t="inlineStr">
+      <c r="C8" s="69" t="inlineStr">
         <is>
           <t>曾心越</t>
         </is>
       </c>
-      <c r="D8" s="33" t="n">
+      <c r="D8" s="69" t="n">
         <v>30</v>
       </c>
-      <c r="E8" s="33" t="inlineStr">
+      <c r="E8" s="69" t="inlineStr">
         <is>
           <t>国际商学院</t>
         </is>
       </c>
-      <c r="F8" s="33" t="inlineStr">
+      <c r="F8" s="69" t="inlineStr">
         <is>
           <t>金融学（中外合作办学）</t>
         </is>
       </c>
-      <c r="G8" s="33" t="inlineStr">
+      <c r="G8" s="69" t="inlineStr">
         <is>
           <t>本科</t>
         </is>
       </c>
-      <c r="H8" s="33" t="n">
+      <c r="H8" s="69" t="n">
         <v>2023</v>
       </c>
-      <c r="I8" s="33" t="n">
+      <c r="I8" s="69" t="n">
         <v>711</v>
       </c>
-      <c r="J8" s="34" t="n"/>
+      <c r="J8" s="70" t="n"/>
     </row>
     <row r="9" ht="24" customFormat="1" customHeight="1" s="1">
-      <c r="A9" s="32" t="n">
+      <c r="A9" s="68" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="33" t="inlineStr">
+      <c r="B9" s="69" t="inlineStr">
         <is>
           <t>20233501037</t>
         </is>
       </c>
-      <c r="C9" s="33" t="inlineStr">
+      <c r="C9" s="69" t="inlineStr">
         <is>
           <t>李贤</t>
         </is>
       </c>
-      <c r="D9" s="33" t="n">
+      <c r="D9" s="69" t="n">
         <v>30</v>
       </c>
-      <c r="E9" s="33" t="inlineStr">
+      <c r="E9" s="69" t="inlineStr">
         <is>
           <t>国际商学院</t>
         </is>
       </c>
-      <c r="F9" s="33" t="inlineStr">
+      <c r="F9" s="69" t="inlineStr">
         <is>
           <t>文化产业管理</t>
         </is>
       </c>
-      <c r="G9" s="33" t="inlineStr">
+      <c r="G9" s="69" t="inlineStr">
         <is>
           <t>本科</t>
         </is>
       </c>
-      <c r="H9" s="33" t="n">
+      <c r="H9" s="69" t="n">
         <v>2023</v>
       </c>
-      <c r="I9" s="33" t="n">
+      <c r="I9" s="69" t="n">
         <v>711</v>
       </c>
-      <c r="J9" s="34" t="n"/>
+      <c r="J9" s="70" t="n"/>
     </row>
     <row r="10" ht="24" customFormat="1" customHeight="1" s="1">
-      <c r="A10" s="32" t="n">
+      <c r="A10" s="68" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="33" t="inlineStr">
+      <c r="B10" s="69" t="inlineStr">
         <is>
           <t>20233502092</t>
         </is>
       </c>
-      <c r="C10" s="33" t="inlineStr">
+      <c r="C10" s="69" t="inlineStr">
         <is>
           <t>毛紫薇</t>
         </is>
       </c>
-      <c r="D10" s="33" t="n">
+      <c r="D10" s="69" t="n">
         <v>30</v>
       </c>
-      <c r="E10" s="33" t="inlineStr">
+      <c r="E10" s="69" t="inlineStr">
         <is>
           <t>国际商学院</t>
         </is>
       </c>
-      <c r="F10" s="33" t="inlineStr">
+      <c r="F10" s="69" t="inlineStr">
         <is>
           <t>网络与新媒体</t>
         </is>
       </c>
-      <c r="G10" s="33" t="inlineStr">
+      <c r="G10" s="69" t="inlineStr">
         <is>
           <t>本科</t>
         </is>
       </c>
-      <c r="H10" s="33" t="n">
+      <c r="H10" s="69" t="n">
         <v>2023</v>
       </c>
-      <c r="I10" s="33" t="n">
+      <c r="I10" s="69" t="n">
         <v>711</v>
       </c>
-      <c r="J10" s="34" t="n"/>
+      <c r="J10" s="70" t="n"/>
     </row>
     <row r="11" ht="24" customFormat="1" customHeight="1" s="1">
-      <c r="A11" s="32" t="n">
+      <c r="A11" s="68" t="n">
         <v>6</v>
       </c>
-      <c r="B11" s="33" t="inlineStr">
+      <c r="B11" s="69" t="inlineStr">
         <is>
           <t>20233502082</t>
         </is>
       </c>
-      <c r="C11" s="33" t="inlineStr">
+      <c r="C11" s="69" t="inlineStr">
         <is>
           <t>冯恋晶</t>
         </is>
       </c>
-      <c r="D11" s="33" t="n">
+      <c r="D11" s="69" t="n">
         <v>26</v>
       </c>
-      <c r="E11" s="33" t="inlineStr">
+      <c r="E11" s="69" t="inlineStr">
         <is>
           <t>国际商学院</t>
         </is>
       </c>
-      <c r="F11" s="33" t="inlineStr">
+      <c r="F11" s="69" t="inlineStr">
         <is>
           <t>网络与新媒体</t>
         </is>
       </c>
-      <c r="G11" s="33" t="inlineStr">
+      <c r="G11" s="69" t="inlineStr">
         <is>
           <t>本科</t>
         </is>
       </c>
-      <c r="H11" s="33" t="n">
+      <c r="H11" s="69" t="n">
         <v>2023</v>
       </c>
-      <c r="I11" s="33" t="n">
+      <c r="I11" s="69" t="n">
         <v>616.2</v>
       </c>
-      <c r="J11" s="34" t="n"/>
+      <c r="J11" s="70" t="n"/>
     </row>
     <row r="12" ht="24" customFormat="1" customHeight="1" s="1">
-      <c r="A12" s="32" t="n">
+      <c r="A12" s="68" t="n">
         <v>7</v>
       </c>
-      <c r="B12" s="33" t="inlineStr">
+      <c r="B12" s="69" t="inlineStr">
         <is>
           <t>20253638110</t>
         </is>
       </c>
-      <c r="C12" s="33" t="inlineStr">
+      <c r="C12" s="69" t="inlineStr">
         <is>
           <t>王文琪</t>
         </is>
       </c>
-      <c r="D12" s="33" t="n">
+      <c r="D12" s="69" t="n">
         <v>30</v>
       </c>
-      <c r="E12" s="33" t="inlineStr">
+      <c r="E12" s="69" t="inlineStr">
         <is>
           <t>国际商学院</t>
         </is>
       </c>
-      <c r="F12" s="33" t="inlineStr">
+      <c r="F12" s="69" t="inlineStr">
         <is>
           <t>大数据管理与应用（中外联合培养）</t>
         </is>
       </c>
-      <c r="G12" s="33" t="inlineStr">
+      <c r="G12" s="69" t="inlineStr">
         <is>
           <t>本科</t>
         </is>
       </c>
-      <c r="H12" s="33" t="n">
+      <c r="H12" s="69" t="n">
         <v>2025</v>
       </c>
-      <c r="I12" s="33" t="n">
+      <c r="I12" s="69" t="n">
         <v>711</v>
       </c>
-      <c r="J12" s="34" t="n"/>
+      <c r="J12" s="70" t="n"/>
     </row>
     <row r="13" ht="24" customFormat="1" customHeight="1" s="1">
-      <c r="A13" s="32" t="n"/>
-      <c r="B13" s="35" t="n"/>
-      <c r="C13" s="35" t="n"/>
-      <c r="D13" s="35" t="n"/>
-      <c r="E13" s="35" t="n"/>
-      <c r="F13" s="35" t="n"/>
-      <c r="G13" s="35" t="n"/>
-      <c r="H13" s="35" t="n"/>
-      <c r="I13" s="35" t="n"/>
-      <c r="J13" s="36" t="n"/>
+      <c r="A13" s="68" t="n"/>
+      <c r="B13" s="71" t="n"/>
+      <c r="C13" s="71" t="n"/>
+      <c r="D13" s="71" t="n"/>
+      <c r="E13" s="71" t="n"/>
+      <c r="F13" s="71" t="n"/>
+      <c r="G13" s="71" t="n"/>
+      <c r="H13" s="71" t="n"/>
+      <c r="I13" s="71" t="n"/>
+      <c r="J13" s="72" t="n"/>
     </row>
     <row r="14" ht="24" customFormat="1" customHeight="1" s="1">
-      <c r="A14" s="37" t="inlineStr">
+      <c r="A14" s="73" t="inlineStr">
         <is>
           <t xml:space="preserve">                                                                                        合计：</t>
         </is>
       </c>
-      <c r="B14" s="37" t="n"/>
-      <c r="C14" s="37" t="n"/>
-      <c r="D14" s="37" t="n"/>
-      <c r="E14" s="37" t="n"/>
-      <c r="F14" s="37" t="n"/>
-      <c r="G14" s="37" t="n"/>
-      <c r="H14" s="37" t="n"/>
-      <c r="I14" s="40">
+      <c r="B14" s="74" t="n"/>
+      <c r="C14" s="74" t="n"/>
+      <c r="D14" s="74" t="n"/>
+      <c r="E14" s="74" t="n"/>
+      <c r="F14" s="74" t="n"/>
+      <c r="G14" s="74" t="n"/>
+      <c r="H14" s="75" t="n"/>
+      <c r="I14" s="76">
         <f>SUM(I6:I13)</f>
         <v/>
       </c>
-      <c r="J14" s="36" t="n"/>
+      <c r="J14" s="72" t="n"/>
     </row>
     <row r="15" ht="55.95" customFormat="1" customHeight="1" s="1">
-      <c r="A15" s="41" t="inlineStr">
+      <c r="A15" s="77" t="inlineStr">
         <is>
           <t>设岗单位负责人签字：                制表人签字：                制表人电话：              制表日期：2026年3月2日</t>
         </is>
       </c>
-      <c r="B15" s="41" t="n"/>
-      <c r="C15" s="41" t="n"/>
-      <c r="D15" s="41" t="n"/>
-      <c r="E15" s="41" t="n"/>
-      <c r="F15" s="41" t="n"/>
-      <c r="G15" s="41" t="n"/>
-      <c r="H15" s="41" t="n"/>
-      <c r="I15" s="41" t="n"/>
-      <c r="J15" s="41" t="n"/>
+      <c r="B15" s="77" t="n"/>
+      <c r="C15" s="77" t="n"/>
+      <c r="D15" s="77" t="n"/>
+      <c r="E15" s="77" t="n"/>
+      <c r="F15" s="77" t="n"/>
+      <c r="G15" s="77" t="n"/>
+      <c r="H15" s="77" t="n"/>
+      <c r="I15" s="77" t="n"/>
+      <c r="J15" s="77" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">
